--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrInvestBondInfo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrInvestBondInfo004MTM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\joyinwork\bs2.1.2\2.1.2\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\CQ-TZJY-0930\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -181,15 +181,6 @@
     <t>02:T+1</t>
   </si>
   <si>
-    <t>AC:摊余成本类</t>
-  </si>
-  <si>
-    <t>FVOCI:公允价值变动计入其他综合收益</t>
-  </si>
-  <si>
-    <t>FVTPL:公允价值变动计入当期损益</t>
-  </si>
-  <si>
     <t>PRM01:指定价格</t>
   </si>
   <si>
@@ -285,6 +276,18 @@
   </si>
   <si>
     <t>交易对手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC:以收取该金融资产合同现金流量为目的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FVOCI:以收取该合同现金流量及出售金融资产为目的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FVTPL:以出售该金融资产为目的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -639,7 +642,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -648,34 +651,34 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N1" t="s">
         <v>10</v>
       </c>
       <c r="O1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="R1" t="s">
         <v>13</v>
@@ -684,7 +687,7 @@
         <v>14</v>
       </c>
       <c r="T1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="U1" t="s">
         <v>15</v>
@@ -794,13 +797,13 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
         <v>76</v>
-      </c>
-      <c r="L1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" t="s">
-        <v>79</v>
       </c>
       <c r="N1" t="s">
         <v>10</v>
@@ -809,7 +812,7 @@
         <v>11</v>
       </c>
       <c r="P1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q1" t="s">
         <v>12</v>
@@ -821,7 +824,7 @@
         <v>14</v>
       </c>
       <c r="T1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="U1" t="s">
         <v>15</v>
@@ -835,19 +838,19 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s">
         <v>49</v>
       </c>
       <c r="O2" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="P2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Q2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.15">
@@ -858,19 +861,19 @@
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N3" t="s">
         <v>50</v>
       </c>
       <c r="O3" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="P3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.15">
@@ -881,16 +884,16 @@
         <v>18</v>
       </c>
       <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O4" t="s">
+        <v>81</v>
+      </c>
+      <c r="P4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" t="s">
         <v>56</v>
-      </c>
-      <c r="O4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.15">
@@ -898,10 +901,10 @@
         <v>19</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
@@ -909,10 +912,10 @@
         <v>20</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.15">
@@ -920,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="Q7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.15">
